--- a/Resultados/RGAA/ibnr_rgaa_RC daños a cosas.xlsx
+++ b/Resultados/RGAA/ibnr_rgaa_RC daños a cosas.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\Documents\Python Script\Github\IBNR-NIIF-17\Resultados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\Python_script\Github\IBNR-NIIF-17\Resultados\RGAA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C6801F6-C531-4D02-B1F7-D875DEFD3759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF318F5-20EB-4B4C-91BA-DBD8F53C1AC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$11:$B$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$I$20:$I$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,8 +58,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="yyyy"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="yyyy"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -216,18 +216,9 @@
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -238,6 +229,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -540,140 +540,164 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="F6:J12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="F6:L12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="6:10" x14ac:dyDescent="0.3">
-      <c r="F6" s="14" t="s">
+    <row r="6" spans="6:12" x14ac:dyDescent="0.25">
+      <c r="F6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="6:12" x14ac:dyDescent="0.25">
       <c r="F7" s="1">
         <v>43101</v>
       </c>
-      <c r="G7" s="2">
-        <v>1050.9423031129511</v>
-      </c>
-      <c r="H7" s="3">
+      <c r="G7" s="6">
+        <v>887.56050124498256</v>
+      </c>
+      <c r="H7" s="7">
         <v>1.05</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="6">
         <f>H7*G7</f>
-        <v>1103.4894182685987</v>
-      </c>
-      <c r="J7" s="4">
-        <v>52.547115155647582</v>
+        <v>931.93852630723177</v>
+      </c>
+      <c r="J7" s="8">
+        <f>I7-G7</f>
+        <v>44.378025062249208</v>
+      </c>
+      <c r="L7">
+        <v>44.378025062249137</v>
       </c>
     </row>
-    <row r="8" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="6:12" x14ac:dyDescent="0.25">
       <c r="F8" s="1">
         <v>43466</v>
       </c>
-      <c r="G8" s="5">
-        <v>813.03049648893818</v>
-      </c>
-      <c r="H8" s="6">
-        <v>1.0601091924096682</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" ref="I8:I12" si="0">H8*G8</f>
-        <v>861.90110303731979</v>
-      </c>
-      <c r="J8" s="7">
-        <v>48.870606548381232</v>
+      <c r="G8" s="9">
+        <v>715.29381828606074</v>
+      </c>
+      <c r="H8" s="10">
+        <v>1.058015183978948</v>
+      </c>
+      <c r="I8" s="9">
+        <f>H8*G8</f>
+        <v>756.7917207529307</v>
+      </c>
+      <c r="J8" s="11">
+        <f t="shared" ref="J8:J12" si="0">I8-G8</f>
+        <v>41.497902466869959</v>
+      </c>
+      <c r="L8">
+        <v>41.497902466870357</v>
       </c>
     </row>
-    <row r="9" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="6:12" x14ac:dyDescent="0.25">
       <c r="F9" s="1">
         <v>43831</v>
       </c>
-      <c r="G9" s="5">
-        <v>833.96204787301167</v>
-      </c>
-      <c r="H9" s="6">
-        <v>1.0749339868501857</v>
-      </c>
-      <c r="I9" s="5">
+      <c r="G9" s="9">
+        <v>676.60919012342549</v>
+      </c>
+      <c r="H9" s="10">
+        <v>1.0698298064980707</v>
+      </c>
+      <c r="I9" s="9">
+        <f t="shared" ref="I8:I12" si="1">H9*G9</f>
+        <v>723.8566789445606</v>
+      </c>
+      <c r="J9" s="11">
         <f t="shared" si="0"/>
-        <v>896.45414900188189</v>
-      </c>
-      <c r="J9" s="7">
-        <v>62.492101128869507</v>
+        <v>47.247488821135107</v>
+      </c>
+      <c r="L9">
+        <v>47.247488821135377</v>
       </c>
     </row>
-    <row r="10" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="6:12" x14ac:dyDescent="0.25">
       <c r="F10" s="1">
         <v>44197</v>
       </c>
-      <c r="G10" s="5">
-        <v>944.04307322647105</v>
-      </c>
-      <c r="H10" s="6">
-        <v>1.0926376810297369</v>
-      </c>
-      <c r="I10" s="5">
+      <c r="G10" s="9">
+        <v>709.39091300716689</v>
+      </c>
+      <c r="H10" s="10">
+        <v>1.0854471227700973</v>
+      </c>
+      <c r="I10" s="9">
+        <f t="shared" si="1"/>
+        <v>770.00632544288169</v>
+      </c>
+      <c r="J10" s="11">
         <f t="shared" si="0"/>
-        <v>1031.4970343223574</v>
-      </c>
-      <c r="J10" s="7">
-        <v>87.453961095885134</v>
+        <v>60.615412435714802</v>
+      </c>
+      <c r="L10">
+        <v>60.615412435715463</v>
       </c>
     </row>
-    <row r="11" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="6:12" x14ac:dyDescent="0.25">
       <c r="F11" s="1">
         <v>44562</v>
       </c>
-      <c r="G11" s="5">
-        <v>708.55640285746904</v>
-      </c>
-      <c r="H11" s="6">
-        <v>1.1339329017356725</v>
-      </c>
-      <c r="I11" s="5">
+      <c r="G11" s="9">
+        <v>495.51085642410942</v>
+      </c>
+      <c r="H11" s="10">
+        <v>1.1219467173038393</v>
+      </c>
+      <c r="I11" s="9">
+        <f t="shared" si="1"/>
+        <v>555.9367787534436</v>
+      </c>
+      <c r="J11" s="11">
         <f t="shared" si="0"/>
-        <v>803.45541793556004</v>
-      </c>
-      <c r="J11" s="7">
-        <v>94.899015078089846</v>
+        <v>60.425922329334185</v>
+      </c>
+      <c r="L11">
+        <v>60.425922329334348</v>
       </c>
     </row>
-    <row r="12" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="6:12" x14ac:dyDescent="0.25">
       <c r="F12" s="1">
         <v>44927</v>
       </c>
-      <c r="G12" s="8">
-        <v>534.07327667766071</v>
-      </c>
-      <c r="H12" s="9">
-        <v>1.360077811557945</v>
-      </c>
-      <c r="I12" s="8">
+      <c r="G12" s="12">
+        <v>358.323815174</v>
+      </c>
+      <c r="H12" s="13">
+        <v>1.3401150008245963</v>
+      </c>
+      <c r="I12" s="12">
+        <f t="shared" si="1"/>
+        <v>480.19511986737751</v>
+      </c>
+      <c r="J12" s="14">
         <f t="shared" si="0"/>
-        <v>726.38121335533367</v>
-      </c>
-      <c r="J12" s="10">
-        <v>192.30793667767179</v>
+        <v>121.87130469337751</v>
+      </c>
+      <c r="L12">
+        <v>121.8713046933775</v>
       </c>
     </row>
   </sheetData>
